--- a/data/DOC abs Grab/Hickory_3_30_26_6_12pm.xlsx
+++ b/data/DOC abs Grab/Hickory_3_30_26_6_12pm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\DM3PEPF00025C39\EXCELCNV\97b668cf-9bb0-48d6-837f-c49ef6039f91\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{82D4153B-6EA9-49FC-8678-671F93FEF123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B67B6DA6-3EF9-4FEB-9B62-19DCBCB421E3}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{82D4153B-6EA9-49FC-8678-671F93FEF123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D756244E-CDFF-4745-8EB2-E683087A1CF3}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{1A81607F-DCD1-4609-A3CB-046BD652E62E}"/>
   </bookViews>
@@ -36,27 +36,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="6">
   <si>
     <t>Wavelength(nm)</t>
   </si>
   <si>
-    <t>Sample 1(Abs)</t>
+    <t>DS_abs</t>
   </si>
   <si>
-    <t>Sample 2(Abs)</t>
-  </si>
-  <si>
-    <t>Sample 3(Abs)</t>
-  </si>
-  <si>
-    <t>Sample 4(Abs)</t>
-  </si>
-  <si>
-    <t>Sample 5(Abs)</t>
-  </si>
-  <si>
-    <t>Sample 6(Abs)</t>
+    <t>US_abs</t>
   </si>
   <si>
     <t>Date</t>
@@ -910,6 +898,8 @@
   <dimension ref="A1:I457"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
     <col min="8" max="8" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -921,25 +911,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -968,7 +958,7 @@
         <v>46111</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -997,7 +987,7 @@
         <v>46111</v>
       </c>
       <c r="I3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1026,7 +1016,7 @@
         <v>46111</v>
       </c>
       <c r="I4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1055,7 +1045,7 @@
         <v>46111</v>
       </c>
       <c r="I5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1084,7 +1074,7 @@
         <v>46111</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1113,7 +1103,7 @@
         <v>46111</v>
       </c>
       <c r="I7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1142,7 +1132,7 @@
         <v>46111</v>
       </c>
       <c r="I8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1171,7 +1161,7 @@
         <v>46111</v>
       </c>
       <c r="I9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1200,7 +1190,7 @@
         <v>46111</v>
       </c>
       <c r="I10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1229,7 +1219,7 @@
         <v>46111</v>
       </c>
       <c r="I11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1258,7 +1248,7 @@
         <v>46111</v>
       </c>
       <c r="I12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1287,7 +1277,7 @@
         <v>46111</v>
       </c>
       <c r="I13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1316,7 +1306,7 @@
         <v>46111</v>
       </c>
       <c r="I14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1345,7 +1335,7 @@
         <v>46111</v>
       </c>
       <c r="I15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1374,7 +1364,7 @@
         <v>46111</v>
       </c>
       <c r="I16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1403,7 +1393,7 @@
         <v>46111</v>
       </c>
       <c r="I17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1432,7 +1422,7 @@
         <v>46111</v>
       </c>
       <c r="I18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1461,7 +1451,7 @@
         <v>46111</v>
       </c>
       <c r="I19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1490,7 +1480,7 @@
         <v>46111</v>
       </c>
       <c r="I20" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1519,7 +1509,7 @@
         <v>46111</v>
       </c>
       <c r="I21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1548,7 +1538,7 @@
         <v>46111</v>
       </c>
       <c r="I22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1577,7 +1567,7 @@
         <v>46111</v>
       </c>
       <c r="I23" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1606,7 +1596,7 @@
         <v>46111</v>
       </c>
       <c r="I24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1635,7 +1625,7 @@
         <v>46111</v>
       </c>
       <c r="I25" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1664,7 +1654,7 @@
         <v>46111</v>
       </c>
       <c r="I26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1693,7 +1683,7 @@
         <v>46111</v>
       </c>
       <c r="I27" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1722,7 +1712,7 @@
         <v>46111</v>
       </c>
       <c r="I28" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1751,7 +1741,7 @@
         <v>46111</v>
       </c>
       <c r="I29" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1780,7 +1770,7 @@
         <v>46111</v>
       </c>
       <c r="I30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1809,7 +1799,7 @@
         <v>46111</v>
       </c>
       <c r="I31" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1838,7 +1828,7 @@
         <v>46111</v>
       </c>
       <c r="I32" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1867,7 +1857,7 @@
         <v>46111</v>
       </c>
       <c r="I33" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1896,7 +1886,7 @@
         <v>46111</v>
       </c>
       <c r="I34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1925,7 +1915,7 @@
         <v>46111</v>
       </c>
       <c r="I35" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1954,7 +1944,7 @@
         <v>46111</v>
       </c>
       <c r="I36" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1983,7 +1973,7 @@
         <v>46111</v>
       </c>
       <c r="I37" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2012,7 +2002,7 @@
         <v>46111</v>
       </c>
       <c r="I38" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2041,7 +2031,7 @@
         <v>46111</v>
       </c>
       <c r="I39" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2070,7 +2060,7 @@
         <v>46111</v>
       </c>
       <c r="I40" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2099,7 +2089,7 @@
         <v>46111</v>
       </c>
       <c r="I41" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2128,7 +2118,7 @@
         <v>46111</v>
       </c>
       <c r="I42" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2157,7 +2147,7 @@
         <v>46111</v>
       </c>
       <c r="I43" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2186,7 +2176,7 @@
         <v>46111</v>
       </c>
       <c r="I44" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2215,7 +2205,7 @@
         <v>46111</v>
       </c>
       <c r="I45" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2244,7 +2234,7 @@
         <v>46111</v>
       </c>
       <c r="I46" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2273,7 +2263,7 @@
         <v>46111</v>
       </c>
       <c r="I47" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2302,7 +2292,7 @@
         <v>46111</v>
       </c>
       <c r="I48" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2331,7 +2321,7 @@
         <v>46111</v>
       </c>
       <c r="I49" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2360,7 +2350,7 @@
         <v>46111</v>
       </c>
       <c r="I50" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2389,7 +2379,7 @@
         <v>46111</v>
       </c>
       <c r="I51" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2418,7 +2408,7 @@
         <v>46111</v>
       </c>
       <c r="I52" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2447,7 +2437,7 @@
         <v>46111</v>
       </c>
       <c r="I53" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2476,7 +2466,7 @@
         <v>46111</v>
       </c>
       <c r="I54" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2505,7 +2495,7 @@
         <v>46111</v>
       </c>
       <c r="I55" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2534,7 +2524,7 @@
         <v>46111</v>
       </c>
       <c r="I56" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2563,7 +2553,7 @@
         <v>46111</v>
       </c>
       <c r="I57" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2592,7 +2582,7 @@
         <v>46111</v>
       </c>
       <c r="I58" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2621,7 +2611,7 @@
         <v>46111</v>
       </c>
       <c r="I59" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2650,7 +2640,7 @@
         <v>46111</v>
       </c>
       <c r="I60" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2679,7 +2669,7 @@
         <v>46111</v>
       </c>
       <c r="I61" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2708,7 +2698,7 @@
         <v>46111</v>
       </c>
       <c r="I62" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2737,7 +2727,7 @@
         <v>46111</v>
       </c>
       <c r="I63" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2766,7 +2756,7 @@
         <v>46111</v>
       </c>
       <c r="I64" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2795,7 +2785,7 @@
         <v>46111</v>
       </c>
       <c r="I65" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2824,7 +2814,7 @@
         <v>46111</v>
       </c>
       <c r="I66" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2853,7 +2843,7 @@
         <v>46111</v>
       </c>
       <c r="I67" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2882,7 +2872,7 @@
         <v>46111</v>
       </c>
       <c r="I68" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2911,7 +2901,7 @@
         <v>46111</v>
       </c>
       <c r="I69" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2940,7 +2930,7 @@
         <v>46111</v>
       </c>
       <c r="I70" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2969,7 +2959,7 @@
         <v>46111</v>
       </c>
       <c r="I71" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2998,7 +2988,7 @@
         <v>46111</v>
       </c>
       <c r="I72" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3027,7 +3017,7 @@
         <v>46111</v>
       </c>
       <c r="I73" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3056,7 +3046,7 @@
         <v>46111</v>
       </c>
       <c r="I74" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3085,7 +3075,7 @@
         <v>46111</v>
       </c>
       <c r="I75" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3114,7 +3104,7 @@
         <v>46111</v>
       </c>
       <c r="I76" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3143,7 +3133,7 @@
         <v>46111</v>
       </c>
       <c r="I77" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3172,7 +3162,7 @@
         <v>46111</v>
       </c>
       <c r="I78" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -3201,7 +3191,7 @@
         <v>46111</v>
       </c>
       <c r="I79" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3230,7 +3220,7 @@
         <v>46111</v>
       </c>
       <c r="I80" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3259,7 +3249,7 @@
         <v>46111</v>
       </c>
       <c r="I81" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3288,7 +3278,7 @@
         <v>46111</v>
       </c>
       <c r="I82" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3317,7 +3307,7 @@
         <v>46111</v>
       </c>
       <c r="I83" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3346,7 +3336,7 @@
         <v>46111</v>
       </c>
       <c r="I84" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3375,7 +3365,7 @@
         <v>46111</v>
       </c>
       <c r="I85" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -3404,7 +3394,7 @@
         <v>46111</v>
       </c>
       <c r="I86" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3433,7 +3423,7 @@
         <v>46111</v>
       </c>
       <c r="I87" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -3462,7 +3452,7 @@
         <v>46111</v>
       </c>
       <c r="I88" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3491,7 +3481,7 @@
         <v>46111</v>
       </c>
       <c r="I89" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3520,7 +3510,7 @@
         <v>46111</v>
       </c>
       <c r="I90" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3549,7 +3539,7 @@
         <v>46111</v>
       </c>
       <c r="I91" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -3578,7 +3568,7 @@
         <v>46111</v>
       </c>
       <c r="I92" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3607,7 +3597,7 @@
         <v>46111</v>
       </c>
       <c r="I93" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3636,7 +3626,7 @@
         <v>46111</v>
       </c>
       <c r="I94" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3665,7 +3655,7 @@
         <v>46111</v>
       </c>
       <c r="I95" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3694,7 +3684,7 @@
         <v>46111</v>
       </c>
       <c r="I96" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3723,7 +3713,7 @@
         <v>46111</v>
       </c>
       <c r="I97" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3752,7 +3742,7 @@
         <v>46111</v>
       </c>
       <c r="I98" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3781,7 +3771,7 @@
         <v>46111</v>
       </c>
       <c r="I99" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3810,7 +3800,7 @@
         <v>46111</v>
       </c>
       <c r="I100" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3839,7 +3829,7 @@
         <v>46111</v>
       </c>
       <c r="I101" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3868,7 +3858,7 @@
         <v>46111</v>
       </c>
       <c r="I102" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3897,7 +3887,7 @@
         <v>46111</v>
       </c>
       <c r="I103" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3926,7 +3916,7 @@
         <v>46111</v>
       </c>
       <c r="I104" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3955,7 +3945,7 @@
         <v>46111</v>
       </c>
       <c r="I105" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3984,7 +3974,7 @@
         <v>46111</v>
       </c>
       <c r="I106" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -4013,7 +4003,7 @@
         <v>46111</v>
       </c>
       <c r="I107" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -4042,7 +4032,7 @@
         <v>46111</v>
       </c>
       <c r="I108" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -4071,7 +4061,7 @@
         <v>46111</v>
       </c>
       <c r="I109" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -4100,7 +4090,7 @@
         <v>46111</v>
       </c>
       <c r="I110" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -4129,7 +4119,7 @@
         <v>46111</v>
       </c>
       <c r="I111" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -4158,7 +4148,7 @@
         <v>46111</v>
       </c>
       <c r="I112" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -4187,7 +4177,7 @@
         <v>46111</v>
       </c>
       <c r="I113" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -4216,7 +4206,7 @@
         <v>46111</v>
       </c>
       <c r="I114" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4245,7 +4235,7 @@
         <v>46111</v>
       </c>
       <c r="I115" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4274,7 +4264,7 @@
         <v>46111</v>
       </c>
       <c r="I116" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -4303,7 +4293,7 @@
         <v>46111</v>
       </c>
       <c r="I117" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -4332,7 +4322,7 @@
         <v>46111</v>
       </c>
       <c r="I118" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -4361,7 +4351,7 @@
         <v>46111</v>
       </c>
       <c r="I119" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -4390,7 +4380,7 @@
         <v>46111</v>
       </c>
       <c r="I120" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -4419,7 +4409,7 @@
         <v>46111</v>
       </c>
       <c r="I121" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -4448,7 +4438,7 @@
         <v>46111</v>
       </c>
       <c r="I122" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -4477,7 +4467,7 @@
         <v>46111</v>
       </c>
       <c r="I123" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -4506,7 +4496,7 @@
         <v>46111</v>
       </c>
       <c r="I124" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -4535,7 +4525,7 @@
         <v>46111</v>
       </c>
       <c r="I125" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -4564,7 +4554,7 @@
         <v>46111</v>
       </c>
       <c r="I126" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -4593,7 +4583,7 @@
         <v>46111</v>
       </c>
       <c r="I127" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -4622,7 +4612,7 @@
         <v>46111</v>
       </c>
       <c r="I128" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -4651,7 +4641,7 @@
         <v>46111</v>
       </c>
       <c r="I129" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -4680,7 +4670,7 @@
         <v>46111</v>
       </c>
       <c r="I130" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -4709,7 +4699,7 @@
         <v>46111</v>
       </c>
       <c r="I131" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -4738,7 +4728,7 @@
         <v>46111</v>
       </c>
       <c r="I132" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -4767,7 +4757,7 @@
         <v>46111</v>
       </c>
       <c r="I133" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -4796,7 +4786,7 @@
         <v>46111</v>
       </c>
       <c r="I134" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -4825,7 +4815,7 @@
         <v>46111</v>
       </c>
       <c r="I135" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -4854,7 +4844,7 @@
         <v>46111</v>
       </c>
       <c r="I136" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -4883,7 +4873,7 @@
         <v>46111</v>
       </c>
       <c r="I137" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -4912,7 +4902,7 @@
         <v>46111</v>
       </c>
       <c r="I138" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -4941,7 +4931,7 @@
         <v>46111</v>
       </c>
       <c r="I139" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -4970,7 +4960,7 @@
         <v>46111</v>
       </c>
       <c r="I140" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4999,7 +4989,7 @@
         <v>46111</v>
       </c>
       <c r="I141" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -5028,7 +5018,7 @@
         <v>46111</v>
       </c>
       <c r="I142" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -5057,7 +5047,7 @@
         <v>46111</v>
       </c>
       <c r="I143" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -5086,7 +5076,7 @@
         <v>46111</v>
       </c>
       <c r="I144" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -5115,7 +5105,7 @@
         <v>46111</v>
       </c>
       <c r="I145" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -5144,7 +5134,7 @@
         <v>46111</v>
       </c>
       <c r="I146" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -5173,7 +5163,7 @@
         <v>46111</v>
       </c>
       <c r="I147" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -5202,7 +5192,7 @@
         <v>46111</v>
       </c>
       <c r="I148" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -5231,7 +5221,7 @@
         <v>46111</v>
       </c>
       <c r="I149" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -5260,7 +5250,7 @@
         <v>46111</v>
       </c>
       <c r="I150" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -5289,7 +5279,7 @@
         <v>46111</v>
       </c>
       <c r="I151" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -5318,7 +5308,7 @@
         <v>46111</v>
       </c>
       <c r="I152" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -5347,7 +5337,7 @@
         <v>46111</v>
       </c>
       <c r="I153" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -5376,7 +5366,7 @@
         <v>46111</v>
       </c>
       <c r="I154" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -5405,7 +5395,7 @@
         <v>46111</v>
       </c>
       <c r="I155" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -5434,7 +5424,7 @@
         <v>46111</v>
       </c>
       <c r="I156" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -5463,7 +5453,7 @@
         <v>46111</v>
       </c>
       <c r="I157" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -5492,7 +5482,7 @@
         <v>46111</v>
       </c>
       <c r="I158" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -5521,7 +5511,7 @@
         <v>46111</v>
       </c>
       <c r="I159" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -5550,7 +5540,7 @@
         <v>46111</v>
       </c>
       <c r="I160" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -5579,7 +5569,7 @@
         <v>46111</v>
       </c>
       <c r="I161" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -5608,7 +5598,7 @@
         <v>46111</v>
       </c>
       <c r="I162" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -5637,7 +5627,7 @@
         <v>46111</v>
       </c>
       <c r="I163" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -5666,7 +5656,7 @@
         <v>46111</v>
       </c>
       <c r="I164" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -5695,7 +5685,7 @@
         <v>46111</v>
       </c>
       <c r="I165" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -5724,7 +5714,7 @@
         <v>46111</v>
       </c>
       <c r="I166" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -5753,7 +5743,7 @@
         <v>46111</v>
       </c>
       <c r="I167" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -5782,7 +5772,7 @@
         <v>46111</v>
       </c>
       <c r="I168" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -5811,7 +5801,7 @@
         <v>46111</v>
       </c>
       <c r="I169" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -5840,7 +5830,7 @@
         <v>46111</v>
       </c>
       <c r="I170" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -5869,7 +5859,7 @@
         <v>46111</v>
       </c>
       <c r="I171" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -5898,7 +5888,7 @@
         <v>46111</v>
       </c>
       <c r="I172" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -5927,7 +5917,7 @@
         <v>46111</v>
       </c>
       <c r="I173" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -5956,7 +5946,7 @@
         <v>46111</v>
       </c>
       <c r="I174" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -5985,7 +5975,7 @@
         <v>46111</v>
       </c>
       <c r="I175" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -6014,7 +6004,7 @@
         <v>46111</v>
       </c>
       <c r="I176" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -6043,7 +6033,7 @@
         <v>46111</v>
       </c>
       <c r="I177" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -6072,7 +6062,7 @@
         <v>46111</v>
       </c>
       <c r="I178" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -6101,7 +6091,7 @@
         <v>46111</v>
       </c>
       <c r="I179" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -6130,7 +6120,7 @@
         <v>46111</v>
       </c>
       <c r="I180" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -6159,7 +6149,7 @@
         <v>46111</v>
       </c>
       <c r="I181" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -6188,7 +6178,7 @@
         <v>46111</v>
       </c>
       <c r="I182" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -6217,7 +6207,7 @@
         <v>46111</v>
       </c>
       <c r="I183" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -6246,7 +6236,7 @@
         <v>46111</v>
       </c>
       <c r="I184" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -6275,7 +6265,7 @@
         <v>46111</v>
       </c>
       <c r="I185" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -6304,7 +6294,7 @@
         <v>46111</v>
       </c>
       <c r="I186" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -6333,7 +6323,7 @@
         <v>46111</v>
       </c>
       <c r="I187" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -6362,7 +6352,7 @@
         <v>46111</v>
       </c>
       <c r="I188" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -6391,7 +6381,7 @@
         <v>46111</v>
       </c>
       <c r="I189" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -6420,7 +6410,7 @@
         <v>46111</v>
       </c>
       <c r="I190" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -6449,7 +6439,7 @@
         <v>46111</v>
       </c>
       <c r="I191" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -6478,7 +6468,7 @@
         <v>46111</v>
       </c>
       <c r="I192" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -6507,7 +6497,7 @@
         <v>46111</v>
       </c>
       <c r="I193" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -6536,7 +6526,7 @@
         <v>46111</v>
       </c>
       <c r="I194" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -6565,7 +6555,7 @@
         <v>46111</v>
       </c>
       <c r="I195" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -6594,7 +6584,7 @@
         <v>46111</v>
       </c>
       <c r="I196" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -6623,7 +6613,7 @@
         <v>46111</v>
       </c>
       <c r="I197" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -6652,7 +6642,7 @@
         <v>46111</v>
       </c>
       <c r="I198" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -6681,7 +6671,7 @@
         <v>46111</v>
       </c>
       <c r="I199" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -6710,7 +6700,7 @@
         <v>46111</v>
       </c>
       <c r="I200" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -6739,7 +6729,7 @@
         <v>46111</v>
       </c>
       <c r="I201" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -6768,7 +6758,7 @@
         <v>46111</v>
       </c>
       <c r="I202" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -6797,7 +6787,7 @@
         <v>46111</v>
       </c>
       <c r="I203" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -6826,7 +6816,7 @@
         <v>46111</v>
       </c>
       <c r="I204" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -6855,7 +6845,7 @@
         <v>46111</v>
       </c>
       <c r="I205" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -6884,7 +6874,7 @@
         <v>46111</v>
       </c>
       <c r="I206" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -6913,7 +6903,7 @@
         <v>46111</v>
       </c>
       <c r="I207" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -6942,7 +6932,7 @@
         <v>46111</v>
       </c>
       <c r="I208" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:9">
@@ -6971,7 +6961,7 @@
         <v>46111</v>
       </c>
       <c r="I209" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:9">
@@ -7000,7 +6990,7 @@
         <v>46111</v>
       </c>
       <c r="I210" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -7029,7 +7019,7 @@
         <v>46111</v>
       </c>
       <c r="I211" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -7058,7 +7048,7 @@
         <v>46111</v>
       </c>
       <c r="I212" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:9">
@@ -7087,7 +7077,7 @@
         <v>46111</v>
       </c>
       <c r="I213" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:9">
@@ -7116,7 +7106,7 @@
         <v>46111</v>
       </c>
       <c r="I214" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -7145,7 +7135,7 @@
         <v>46111</v>
       </c>
       <c r="I215" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -7174,7 +7164,7 @@
         <v>46111</v>
       </c>
       <c r="I216" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:9">
@@ -7203,7 +7193,7 @@
         <v>46111</v>
       </c>
       <c r="I217" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:9">
@@ -7232,7 +7222,7 @@
         <v>46111</v>
       </c>
       <c r="I218" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -7261,7 +7251,7 @@
         <v>46111</v>
       </c>
       <c r="I219" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -7290,7 +7280,7 @@
         <v>46111</v>
       </c>
       <c r="I220" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -7319,7 +7309,7 @@
         <v>46111</v>
       </c>
       <c r="I221" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -7348,7 +7338,7 @@
         <v>46111</v>
       </c>
       <c r="I222" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -7377,7 +7367,7 @@
         <v>46111</v>
       </c>
       <c r="I223" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -7406,7 +7396,7 @@
         <v>46111</v>
       </c>
       <c r="I224" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -7435,7 +7425,7 @@
         <v>46111</v>
       </c>
       <c r="I225" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:9">
@@ -7464,7 +7454,7 @@
         <v>46111</v>
       </c>
       <c r="I226" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:9">
@@ -7493,7 +7483,7 @@
         <v>46111</v>
       </c>
       <c r="I227" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:9">
@@ -7522,7 +7512,7 @@
         <v>46111</v>
       </c>
       <c r="I228" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -7551,7 +7541,7 @@
         <v>46111</v>
       </c>
       <c r="I229" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:9">
@@ -7580,7 +7570,7 @@
         <v>46111</v>
       </c>
       <c r="I230" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -7609,7 +7599,7 @@
         <v>46111</v>
       </c>
       <c r="I231" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:9">
@@ -7638,7 +7628,7 @@
         <v>46111</v>
       </c>
       <c r="I232" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:9">
@@ -7667,7 +7657,7 @@
         <v>46111</v>
       </c>
       <c r="I233" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:9">
@@ -7696,7 +7686,7 @@
         <v>46111</v>
       </c>
       <c r="I234" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -7725,7 +7715,7 @@
         <v>46111</v>
       </c>
       <c r="I235" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -7754,7 +7744,7 @@
         <v>46111</v>
       </c>
       <c r="I236" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -7783,7 +7773,7 @@
         <v>46111</v>
       </c>
       <c r="I237" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:9">
@@ -7812,7 +7802,7 @@
         <v>46111</v>
       </c>
       <c r="I238" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -7841,7 +7831,7 @@
         <v>46111</v>
       </c>
       <c r="I239" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -7870,7 +7860,7 @@
         <v>46111</v>
       </c>
       <c r="I240" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -7899,7 +7889,7 @@
         <v>46111</v>
       </c>
       <c r="I241" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -7928,7 +7918,7 @@
         <v>46111</v>
       </c>
       <c r="I242" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -7957,7 +7947,7 @@
         <v>46111</v>
       </c>
       <c r="I243" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -7986,7 +7976,7 @@
         <v>46111</v>
       </c>
       <c r="I244" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:9">
@@ -8015,7 +8005,7 @@
         <v>46111</v>
       </c>
       <c r="I245" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:9">
@@ -8044,7 +8034,7 @@
         <v>46111</v>
       </c>
       <c r="I246" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -8073,7 +8063,7 @@
         <v>46111</v>
       </c>
       <c r="I247" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:9">
@@ -8102,7 +8092,7 @@
         <v>46111</v>
       </c>
       <c r="I248" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -8131,7 +8121,7 @@
         <v>46111</v>
       </c>
       <c r="I249" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:9">
@@ -8160,7 +8150,7 @@
         <v>46111</v>
       </c>
       <c r="I250" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -8189,7 +8179,7 @@
         <v>46111</v>
       </c>
       <c r="I251" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -8218,7 +8208,7 @@
         <v>46111</v>
       </c>
       <c r="I252" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:9">
@@ -8247,7 +8237,7 @@
         <v>46111</v>
       </c>
       <c r="I253" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -8276,7 +8266,7 @@
         <v>46111</v>
       </c>
       <c r="I254" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -8305,7 +8295,7 @@
         <v>46111</v>
       </c>
       <c r="I255" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -8334,7 +8324,7 @@
         <v>46111</v>
       </c>
       <c r="I256" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -8363,7 +8353,7 @@
         <v>46111</v>
       </c>
       <c r="I257" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:9">
@@ -8392,7 +8382,7 @@
         <v>46111</v>
       </c>
       <c r="I258" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:9">
@@ -8421,7 +8411,7 @@
         <v>46111</v>
       </c>
       <c r="I259" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -8450,7 +8440,7 @@
         <v>46111</v>
       </c>
       <c r="I260" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:9">
@@ -8479,7 +8469,7 @@
         <v>46111</v>
       </c>
       <c r="I261" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -8508,7 +8498,7 @@
         <v>46111</v>
       </c>
       <c r="I262" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:9">
@@ -8537,7 +8527,7 @@
         <v>46111</v>
       </c>
       <c r="I263" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:9">
@@ -8566,7 +8556,7 @@
         <v>46111</v>
       </c>
       <c r="I264" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:9">
@@ -8595,7 +8585,7 @@
         <v>46111</v>
       </c>
       <c r="I265" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -8624,7 +8614,7 @@
         <v>46111</v>
       </c>
       <c r="I266" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:9">
@@ -8653,7 +8643,7 @@
         <v>46111</v>
       </c>
       <c r="I267" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:9">
@@ -8682,7 +8672,7 @@
         <v>46111</v>
       </c>
       <c r="I268" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:9">
@@ -8711,7 +8701,7 @@
         <v>46111</v>
       </c>
       <c r="I269" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -8740,7 +8730,7 @@
         <v>46111</v>
       </c>
       <c r="I270" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:9">
@@ -8769,7 +8759,7 @@
         <v>46111</v>
       </c>
       <c r="I271" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:9">
@@ -8798,7 +8788,7 @@
         <v>46111</v>
       </c>
       <c r="I272" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:9">
@@ -8827,7 +8817,7 @@
         <v>46111</v>
       </c>
       <c r="I273" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:9">
@@ -8856,7 +8846,7 @@
         <v>46111</v>
       </c>
       <c r="I274" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:9">
@@ -8885,7 +8875,7 @@
         <v>46111</v>
       </c>
       <c r="I275" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:9">
@@ -8914,7 +8904,7 @@
         <v>46111</v>
       </c>
       <c r="I276" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -8943,7 +8933,7 @@
         <v>46111</v>
       </c>
       <c r="I277" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:9">
@@ -8972,7 +8962,7 @@
         <v>46111</v>
       </c>
       <c r="I278" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:9">
@@ -9001,7 +8991,7 @@
         <v>46111</v>
       </c>
       <c r="I279" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -9030,7 +9020,7 @@
         <v>46111</v>
       </c>
       <c r="I280" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:9">
@@ -9059,7 +9049,7 @@
         <v>46111</v>
       </c>
       <c r="I281" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:9">
@@ -9088,7 +9078,7 @@
         <v>46111</v>
       </c>
       <c r="I282" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:9">
@@ -9117,7 +9107,7 @@
         <v>46111</v>
       </c>
       <c r="I283" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:9">
@@ -9146,7 +9136,7 @@
         <v>46111</v>
       </c>
       <c r="I284" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:9">
@@ -9175,7 +9165,7 @@
         <v>46111</v>
       </c>
       <c r="I285" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:9">
@@ -9204,7 +9194,7 @@
         <v>46111</v>
       </c>
       <c r="I286" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:9">
@@ -9233,7 +9223,7 @@
         <v>46111</v>
       </c>
       <c r="I287" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:9">
@@ -9262,7 +9252,7 @@
         <v>46111</v>
       </c>
       <c r="I288" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:9">
@@ -9291,7 +9281,7 @@
         <v>46111</v>
       </c>
       <c r="I289" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -9320,7 +9310,7 @@
         <v>46111</v>
       </c>
       <c r="I290" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:9">
@@ -9349,7 +9339,7 @@
         <v>46111</v>
       </c>
       <c r="I291" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:9">
@@ -9378,7 +9368,7 @@
         <v>46111</v>
       </c>
       <c r="I292" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:9">
@@ -9407,7 +9397,7 @@
         <v>46111</v>
       </c>
       <c r="I293" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:9">
@@ -9436,7 +9426,7 @@
         <v>46111</v>
       </c>
       <c r="I294" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:9">
@@ -9465,7 +9455,7 @@
         <v>46111</v>
       </c>
       <c r="I295" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296" spans="1:9">
@@ -9494,7 +9484,7 @@
         <v>46111</v>
       </c>
       <c r="I296" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:9">
@@ -9523,7 +9513,7 @@
         <v>46111</v>
       </c>
       <c r="I297" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:9">
@@ -9552,7 +9542,7 @@
         <v>46111</v>
       </c>
       <c r="I298" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:9">
@@ -9581,7 +9571,7 @@
         <v>46111</v>
       </c>
       <c r="I299" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -9610,7 +9600,7 @@
         <v>46111</v>
       </c>
       <c r="I300" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:9">
@@ -9639,7 +9629,7 @@
         <v>46111</v>
       </c>
       <c r="I301" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:9">
@@ -9668,7 +9658,7 @@
         <v>46111</v>
       </c>
       <c r="I302" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:9">
@@ -9697,7 +9687,7 @@
         <v>46111</v>
       </c>
       <c r="I303" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:9">
@@ -9726,7 +9716,7 @@
         <v>46111</v>
       </c>
       <c r="I304" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -9755,7 +9745,7 @@
         <v>46111</v>
       </c>
       <c r="I305" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="306" spans="1:9">
@@ -9784,7 +9774,7 @@
         <v>46111</v>
       </c>
       <c r="I306" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:9">
@@ -9813,7 +9803,7 @@
         <v>46111</v>
       </c>
       <c r="I307" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="308" spans="1:9">
@@ -9842,7 +9832,7 @@
         <v>46111</v>
       </c>
       <c r="I308" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="309" spans="1:9">
@@ -9871,7 +9861,7 @@
         <v>46111</v>
       </c>
       <c r="I309" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:9">
@@ -9900,7 +9890,7 @@
         <v>46111</v>
       </c>
       <c r="I310" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:9">
@@ -9929,7 +9919,7 @@
         <v>46111</v>
       </c>
       <c r="I311" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:9">
@@ -9958,7 +9948,7 @@
         <v>46111</v>
       </c>
       <c r="I312" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:9">
@@ -9987,7 +9977,7 @@
         <v>46111</v>
       </c>
       <c r="I313" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="314" spans="1:9">
@@ -10016,7 +10006,7 @@
         <v>46111</v>
       </c>
       <c r="I314" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315" spans="1:9">
@@ -10045,7 +10035,7 @@
         <v>46111</v>
       </c>
       <c r="I315" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -10074,7 +10064,7 @@
         <v>46111</v>
       </c>
       <c r="I316" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -10103,7 +10093,7 @@
         <v>46111</v>
       </c>
       <c r="I317" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -10132,7 +10122,7 @@
         <v>46111</v>
       </c>
       <c r="I318" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319" spans="1:9">
@@ -10161,7 +10151,7 @@
         <v>46111</v>
       </c>
       <c r="I319" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:9">
@@ -10190,7 +10180,7 @@
         <v>46111</v>
       </c>
       <c r="I320" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="321" spans="1:9">
@@ -10219,7 +10209,7 @@
         <v>46111</v>
       </c>
       <c r="I321" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -10248,7 +10238,7 @@
         <v>46111</v>
       </c>
       <c r="I322" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323" spans="1:9">
@@ -10277,7 +10267,7 @@
         <v>46111</v>
       </c>
       <c r="I323" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -10306,7 +10296,7 @@
         <v>46111</v>
       </c>
       <c r="I324" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -10335,7 +10325,7 @@
         <v>46111</v>
       </c>
       <c r="I325" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:9">
@@ -10364,7 +10354,7 @@
         <v>46111</v>
       </c>
       <c r="I326" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327" spans="1:9">
@@ -10393,7 +10383,7 @@
         <v>46111</v>
       </c>
       <c r="I327" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="328" spans="1:9">
@@ -10422,7 +10412,7 @@
         <v>46111</v>
       </c>
       <c r="I328" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="329" spans="1:9">
@@ -10451,7 +10441,7 @@
         <v>46111</v>
       </c>
       <c r="I329" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="330" spans="1:9">
@@ -10480,7 +10470,7 @@
         <v>46111</v>
       </c>
       <c r="I330" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="331" spans="1:9">
@@ -10509,7 +10499,7 @@
         <v>46111</v>
       </c>
       <c r="I331" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="332" spans="1:9">
@@ -10538,7 +10528,7 @@
         <v>46111</v>
       </c>
       <c r="I332" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="333" spans="1:9">
@@ -10567,7 +10557,7 @@
         <v>46111</v>
       </c>
       <c r="I333" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="334" spans="1:9">
@@ -10596,7 +10586,7 @@
         <v>46111</v>
       </c>
       <c r="I334" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="335" spans="1:9">
@@ -10625,7 +10615,7 @@
         <v>46111</v>
       </c>
       <c r="I335" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="336" spans="1:9">
@@ -10654,7 +10644,7 @@
         <v>46111</v>
       </c>
       <c r="I336" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="337" spans="1:9">
@@ -10683,7 +10673,7 @@
         <v>46111</v>
       </c>
       <c r="I337" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="338" spans="1:9">
@@ -10712,7 +10702,7 @@
         <v>46111</v>
       </c>
       <c r="I338" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="339" spans="1:9">
@@ -10741,7 +10731,7 @@
         <v>46111</v>
       </c>
       <c r="I339" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:9">
@@ -10770,7 +10760,7 @@
         <v>46111</v>
       </c>
       <c r="I340" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="341" spans="1:9">
@@ -10799,7 +10789,7 @@
         <v>46111</v>
       </c>
       <c r="I341" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="342" spans="1:9">
@@ -10828,7 +10818,7 @@
         <v>46111</v>
       </c>
       <c r="I342" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:9">
@@ -10857,7 +10847,7 @@
         <v>46111</v>
       </c>
       <c r="I343" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -10886,7 +10876,7 @@
         <v>46111</v>
       </c>
       <c r="I344" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -10915,7 +10905,7 @@
         <v>46111</v>
       </c>
       <c r="I345" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:9">
@@ -10944,7 +10934,7 @@
         <v>46111</v>
       </c>
       <c r="I346" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:9">
@@ -10973,7 +10963,7 @@
         <v>46111</v>
       </c>
       <c r="I347" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:9">
@@ -11002,7 +10992,7 @@
         <v>46111</v>
       </c>
       <c r="I348" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:9">
@@ -11031,7 +11021,7 @@
         <v>46111</v>
       </c>
       <c r="I349" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:9">
@@ -11060,7 +11050,7 @@
         <v>46111</v>
       </c>
       <c r="I350" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:9">
@@ -11089,7 +11079,7 @@
         <v>46111</v>
       </c>
       <c r="I351" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352" spans="1:9">
@@ -11118,7 +11108,7 @@
         <v>46111</v>
       </c>
       <c r="I352" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:9">
@@ -11147,7 +11137,7 @@
         <v>46111</v>
       </c>
       <c r="I353" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:9">
@@ -11176,7 +11166,7 @@
         <v>46111</v>
       </c>
       <c r="I354" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:9">
@@ -11205,7 +11195,7 @@
         <v>46111</v>
       </c>
       <c r="I355" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:9">
@@ -11234,7 +11224,7 @@
         <v>46111</v>
       </c>
       <c r="I356" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:9">
@@ -11263,7 +11253,7 @@
         <v>46111</v>
       </c>
       <c r="I357" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="358" spans="1:9">
@@ -11292,7 +11282,7 @@
         <v>46111</v>
       </c>
       <c r="I358" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:9">
@@ -11321,7 +11311,7 @@
         <v>46111</v>
       </c>
       <c r="I359" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:9">
@@ -11350,7 +11340,7 @@
         <v>46111</v>
       </c>
       <c r="I360" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:9">
@@ -11379,7 +11369,7 @@
         <v>46111</v>
       </c>
       <c r="I361" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:9">
@@ -11408,7 +11398,7 @@
         <v>46111</v>
       </c>
       <c r="I362" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:9">
@@ -11437,7 +11427,7 @@
         <v>46111</v>
       </c>
       <c r="I363" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:9">
@@ -11466,7 +11456,7 @@
         <v>46111</v>
       </c>
       <c r="I364" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:9">
@@ -11495,7 +11485,7 @@
         <v>46111</v>
       </c>
       <c r="I365" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:9">
@@ -11524,7 +11514,7 @@
         <v>46111</v>
       </c>
       <c r="I366" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:9">
@@ -11553,7 +11543,7 @@
         <v>46111</v>
       </c>
       <c r="I367" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368" spans="1:9">
@@ -11582,7 +11572,7 @@
         <v>46111</v>
       </c>
       <c r="I368" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="369" spans="1:9">
@@ -11611,7 +11601,7 @@
         <v>46111</v>
       </c>
       <c r="I369" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="370" spans="1:9">
@@ -11640,7 +11630,7 @@
         <v>46111</v>
       </c>
       <c r="I370" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:9">
@@ -11669,7 +11659,7 @@
         <v>46111</v>
       </c>
       <c r="I371" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:9">
@@ -11698,7 +11688,7 @@
         <v>46111</v>
       </c>
       <c r="I372" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:9">
@@ -11727,7 +11717,7 @@
         <v>46111</v>
       </c>
       <c r="I373" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="374" spans="1:9">
@@ -11756,7 +11746,7 @@
         <v>46111</v>
       </c>
       <c r="I374" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375" spans="1:9">
@@ -11785,7 +11775,7 @@
         <v>46111</v>
       </c>
       <c r="I375" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="376" spans="1:9">
@@ -11814,7 +11804,7 @@
         <v>46111</v>
       </c>
       <c r="I376" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="377" spans="1:9">
@@ -11843,7 +11833,7 @@
         <v>46111</v>
       </c>
       <c r="I377" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="378" spans="1:9">
@@ -11872,7 +11862,7 @@
         <v>46111</v>
       </c>
       <c r="I378" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="1:9">
@@ -11901,7 +11891,7 @@
         <v>46111</v>
       </c>
       <c r="I379" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:9">
@@ -11930,7 +11920,7 @@
         <v>46111</v>
       </c>
       <c r="I380" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="381" spans="1:9">
@@ -11959,7 +11949,7 @@
         <v>46111</v>
       </c>
       <c r="I381" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:9">
@@ -11988,7 +11978,7 @@
         <v>46111</v>
       </c>
       <c r="I382" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:9">
@@ -12017,7 +12007,7 @@
         <v>46111</v>
       </c>
       <c r="I383" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="384" spans="1:9">
@@ -12046,7 +12036,7 @@
         <v>46111</v>
       </c>
       <c r="I384" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="385" spans="1:9">
@@ -12075,7 +12065,7 @@
         <v>46111</v>
       </c>
       <c r="I385" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="386" spans="1:9">
@@ -12104,7 +12094,7 @@
         <v>46111</v>
       </c>
       <c r="I386" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="387" spans="1:9">
@@ -12133,7 +12123,7 @@
         <v>46111</v>
       </c>
       <c r="I387" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="388" spans="1:9">
@@ -12162,7 +12152,7 @@
         <v>46111</v>
       </c>
       <c r="I388" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="389" spans="1:9">
@@ -12191,7 +12181,7 @@
         <v>46111</v>
       </c>
       <c r="I389" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:9">
@@ -12220,7 +12210,7 @@
         <v>46111</v>
       </c>
       <c r="I390" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391" spans="1:9">
@@ -12249,7 +12239,7 @@
         <v>46111</v>
       </c>
       <c r="I391" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="392" spans="1:9">
@@ -12278,7 +12268,7 @@
         <v>46111</v>
       </c>
       <c r="I392" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="393" spans="1:9">
@@ -12307,7 +12297,7 @@
         <v>46111</v>
       </c>
       <c r="I393" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="394" spans="1:9">
@@ -12336,7 +12326,7 @@
         <v>46111</v>
       </c>
       <c r="I394" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395" spans="1:9">
@@ -12365,7 +12355,7 @@
         <v>46111</v>
       </c>
       <c r="I395" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396" spans="1:9">
@@ -12394,7 +12384,7 @@
         <v>46111</v>
       </c>
       <c r="I396" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="397" spans="1:9">
@@ -12423,7 +12413,7 @@
         <v>46111</v>
       </c>
       <c r="I397" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="398" spans="1:9">
@@ -12452,7 +12442,7 @@
         <v>46111</v>
       </c>
       <c r="I398" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399" spans="1:9">
@@ -12481,7 +12471,7 @@
         <v>46111</v>
       </c>
       <c r="I399" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="400" spans="1:9">
@@ -12510,7 +12500,7 @@
         <v>46111</v>
       </c>
       <c r="I400" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="401" spans="1:9">
@@ -12539,7 +12529,7 @@
         <v>46111</v>
       </c>
       <c r="I401" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="402" spans="1:9">
@@ -12568,7 +12558,7 @@
         <v>46111</v>
       </c>
       <c r="I402" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="403" spans="1:9">
@@ -12597,7 +12587,7 @@
         <v>46111</v>
       </c>
       <c r="I403" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="404" spans="1:9">
@@ -12626,7 +12616,7 @@
         <v>46111</v>
       </c>
       <c r="I404" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="405" spans="1:9">
@@ -12655,7 +12645,7 @@
         <v>46111</v>
       </c>
       <c r="I405" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="406" spans="1:9">
@@ -12684,7 +12674,7 @@
         <v>46111</v>
       </c>
       <c r="I406" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="407" spans="1:9">
@@ -12713,7 +12703,7 @@
         <v>46111</v>
       </c>
       <c r="I407" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="408" spans="1:9">
@@ -12742,7 +12732,7 @@
         <v>46111</v>
       </c>
       <c r="I408" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="409" spans="1:9">
@@ -12771,7 +12761,7 @@
         <v>46111</v>
       </c>
       <c r="I409" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="410" spans="1:9">
@@ -12800,7 +12790,7 @@
         <v>46111</v>
       </c>
       <c r="I410" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="411" spans="1:9">
@@ -12829,7 +12819,7 @@
         <v>46111</v>
       </c>
       <c r="I411" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="412" spans="1:9">
@@ -12858,7 +12848,7 @@
         <v>46111</v>
       </c>
       <c r="I412" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="413" spans="1:9">
@@ -12887,7 +12877,7 @@
         <v>46111</v>
       </c>
       <c r="I413" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="414" spans="1:9">
@@ -12916,7 +12906,7 @@
         <v>46111</v>
       </c>
       <c r="I414" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="415" spans="1:9">
@@ -12945,7 +12935,7 @@
         <v>46111</v>
       </c>
       <c r="I415" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="416" spans="1:9">
@@ -12974,7 +12964,7 @@
         <v>46111</v>
       </c>
       <c r="I416" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="417" spans="1:9">
@@ -13003,7 +12993,7 @@
         <v>46111</v>
       </c>
       <c r="I417" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="418" spans="1:9">
@@ -13032,7 +13022,7 @@
         <v>46111</v>
       </c>
       <c r="I418" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="419" spans="1:9">
@@ -13061,7 +13051,7 @@
         <v>46111</v>
       </c>
       <c r="I419" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="420" spans="1:9">
@@ -13090,7 +13080,7 @@
         <v>46111</v>
       </c>
       <c r="I420" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="421" spans="1:9">
@@ -13119,7 +13109,7 @@
         <v>46111</v>
       </c>
       <c r="I421" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="422" spans="1:9">
@@ -13148,7 +13138,7 @@
         <v>46111</v>
       </c>
       <c r="I422" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="423" spans="1:9">
@@ -13177,7 +13167,7 @@
         <v>46111</v>
       </c>
       <c r="I423" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="424" spans="1:9">
@@ -13206,7 +13196,7 @@
         <v>46111</v>
       </c>
       <c r="I424" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="425" spans="1:9">
@@ -13235,7 +13225,7 @@
         <v>46111</v>
       </c>
       <c r="I425" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="426" spans="1:9">
@@ -13264,7 +13254,7 @@
         <v>46111</v>
       </c>
       <c r="I426" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="427" spans="1:9">
@@ -13293,7 +13283,7 @@
         <v>46111</v>
       </c>
       <c r="I427" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="428" spans="1:9">
@@ -13322,7 +13312,7 @@
         <v>46111</v>
       </c>
       <c r="I428" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="429" spans="1:9">
@@ -13351,7 +13341,7 @@
         <v>46111</v>
       </c>
       <c r="I429" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="430" spans="1:9">
@@ -13380,7 +13370,7 @@
         <v>46111</v>
       </c>
       <c r="I430" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="431" spans="1:9">
@@ -13409,7 +13399,7 @@
         <v>46111</v>
       </c>
       <c r="I431" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="432" spans="1:9">
@@ -13438,7 +13428,7 @@
         <v>46111</v>
       </c>
       <c r="I432" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="433" spans="1:9">
@@ -13467,7 +13457,7 @@
         <v>46111</v>
       </c>
       <c r="I433" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434" spans="1:9">
@@ -13496,7 +13486,7 @@
         <v>46111</v>
       </c>
       <c r="I434" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="435" spans="1:9">
@@ -13525,7 +13515,7 @@
         <v>46111</v>
       </c>
       <c r="I435" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="436" spans="1:9">
@@ -13554,7 +13544,7 @@
         <v>46111</v>
       </c>
       <c r="I436" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="437" spans="1:9">
@@ -13583,7 +13573,7 @@
         <v>46111</v>
       </c>
       <c r="I437" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="438" spans="1:9">
@@ -13612,7 +13602,7 @@
         <v>46111</v>
       </c>
       <c r="I438" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="439" spans="1:9">
@@ -13641,7 +13631,7 @@
         <v>46111</v>
       </c>
       <c r="I439" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440" spans="1:9">
@@ -13670,7 +13660,7 @@
         <v>46111</v>
       </c>
       <c r="I440" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="441" spans="1:9">
@@ -13699,7 +13689,7 @@
         <v>46111</v>
       </c>
       <c r="I441" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="442" spans="1:9">
@@ -13728,7 +13718,7 @@
         <v>46111</v>
       </c>
       <c r="I442" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="443" spans="1:9">
@@ -13757,7 +13747,7 @@
         <v>46111</v>
       </c>
       <c r="I443" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="444" spans="1:9">
@@ -13786,7 +13776,7 @@
         <v>46111</v>
       </c>
       <c r="I444" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="445" spans="1:9">
@@ -13815,7 +13805,7 @@
         <v>46111</v>
       </c>
       <c r="I445" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="446" spans="1:9">
@@ -13844,7 +13834,7 @@
         <v>46111</v>
       </c>
       <c r="I446" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="447" spans="1:9">
@@ -13873,7 +13863,7 @@
         <v>46111</v>
       </c>
       <c r="I447" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="448" spans="1:9">
@@ -13902,7 +13892,7 @@
         <v>46111</v>
       </c>
       <c r="I448" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="449" spans="1:9">
@@ -13931,7 +13921,7 @@
         <v>46111</v>
       </c>
       <c r="I449" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="450" spans="1:9">
@@ -13960,7 +13950,7 @@
         <v>46111</v>
       </c>
       <c r="I450" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="451" spans="1:9">
@@ -13989,7 +13979,7 @@
         <v>46111</v>
       </c>
       <c r="I451" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="452" spans="1:9">
@@ -14018,7 +14008,7 @@
         <v>46111</v>
       </c>
       <c r="I452" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="453" spans="1:9">
@@ -14047,7 +14037,7 @@
         <v>46111</v>
       </c>
       <c r="I453" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="454" spans="1:9">
@@ -14076,7 +14066,7 @@
         <v>46111</v>
       </c>
       <c r="I454" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="455" spans="1:9">
@@ -14105,7 +14095,7 @@
         <v>46111</v>
       </c>
       <c r="I455" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="456" spans="1:9">
@@ -14134,7 +14124,7 @@
         <v>46111</v>
       </c>
       <c r="I456" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="457" spans="1:9">
@@ -14163,7 +14153,7 @@
         <v>46111</v>
       </c>
       <c r="I457" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14172,6 +14162,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Notes1 xmlns="d6d22e61-b5d5-437f-ad8f-227c443f1f4f" xsi:nil="true"/>
@@ -14181,15 +14180,6 @@
     <Notes xmlns="d6d22e61-b5d5-437f-ad8f-227c443f1f4f" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14393,11 +14383,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE091AD2-DA7F-4A90-AB12-21E7F16FB255}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF7209E7-0262-4834-B91A-C76E8D3873C1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF7209E7-0262-4834-B91A-C76E8D3873C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE091AD2-DA7F-4A90-AB12-21E7F16FB255}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
